--- a/static/static_MP_HHScreeningThresholds.xlsx
+++ b/static/static_MP_HHScreeningThresholds.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26529"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\55586\Desktop\tools\access tool\access-tool-migration\static\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\17475\Downloads\RTR2HEM\static\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7F31C54-DE36-447F-80AD-C75037C9553F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C4CB681-D2CA-4782-A1DF-E7E23B6A6E32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8700" yWindow="3255" windowWidth="23070" windowHeight="14910" xr2:uid="{D825EAAC-5B4B-40C5-B153-6DCE7AAAB314}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{D825EAAC-5B4B-40C5-B153-6DCE7AAAB314}"/>
   </bookViews>
   <sheets>
     <sheet name="static" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="21">
   <si>
     <t>Inorganic Arsenic Compounds</t>
   </si>
@@ -96,6 +96,9 @@
   </si>
   <si>
     <t>PB-HAP</t>
+  </si>
+  <si>
+    <t>20250326</t>
   </si>
 </sst>
 </file>
@@ -186,7 +189,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -197,6 +200,9 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -217,9 +223,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -257,7 +263,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -363,7 +369,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -505,7 +511,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -514,17 +520,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{387F162B-1D70-41D6-AA8A-1247799F2CB5}">
   <dimension ref="A1:E6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="32.85546875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="28.42578125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="31.42578125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="19.85546875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="32.88671875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="28.44140625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="31.44140625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="19.88671875" style="1" customWidth="1"/>
     <col min="5" max="5" width="68" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="1"/>
+    <col min="6" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
         <v>19</v>
       </c>
@@ -541,7 +547,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>14</v>
       </c>
@@ -558,7 +564,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>10</v>
       </c>
@@ -575,7 +581,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>9</v>
       </c>
@@ -592,7 +598,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
@@ -609,15 +615,16 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B6" s="3">
-        <v>2.0405999999999999E-4</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>2</v>
+        <f>0.00020406*(1.5/32)</f>
+        <v>9.5653124999999989E-6</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>20</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>1</v>
@@ -629,4 +636,326 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100527F971C14C91B43AC3FED92D7C9BE9C" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="f6636e08f2c4f86f5c2acce8fdd6bec8">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="797d4723-7e88-4c98-a7d1-8e1207631c12" xmlns:ns3="a97c5eaf-f6f2-424c-b1de-d58a88ab7d7b" xmlns:ns4="fa6a9aea-fb0f-4ddd-aff8-712634b7d5fe" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="89d0da6fc7af6b57663ebac9f29cf4af" ns2:_="" ns3:_="" ns4:_="">
+    <xsd:import namespace="797d4723-7e88-4c98-a7d1-8e1207631c12"/>
+    <xsd:import namespace="a97c5eaf-f6f2-424c-b1de-d58a88ab7d7b"/>
+    <xsd:import namespace="fa6a9aea-fb0f-4ddd-aff8-712634b7d5fe"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns4:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:Notes" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="797d4723-7e88-4c98-a7d1-8e1207631c12" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoTags" ma:index="14" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="15" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="16" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="18" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="6856f2ee-118d-42e8-91de-064c9a66b685" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="Notes" ma:index="20" nillable="true" ma:displayName="Notes" ma:format="Dropdown" ma:internalName="Notes">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="21" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="22" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="23" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="25" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="a97c5eaf-f6f2-424c-b1de-d58a88ab7d7b" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="SharedWithUsers" ma:index="12" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:UserMulti">
+            <xsd:sequence>
+              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
+                <xsd:complexType>
+                  <xsd:sequence>
+                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
+                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
+                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
+                  </xsd:sequence>
+                </xsd:complexType>
+              </xsd:element>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithDetails" ma:index="13" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="fa6a9aea-fb0f-4ddd-aff8-712634b7d5fe" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="TaxCatchAll" ma:index="19" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{36eeb0ed-606a-4a98-8f47-fcf9498633dc}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="a97c5eaf-f6f2-424c-b1de-d58a88ab7d7b">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="fa6a9aea-fb0f-4ddd-aff8-712634b7d5fe" xsi:nil="true"/>
+    <Notes xmlns="797d4723-7e88-4c98-a7d1-8e1207631c12" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="797d4723-7e88-4c98-a7d1-8e1207631c12">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC740E37-523E-4806-A02F-119DF69101ED}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="797d4723-7e88-4c98-a7d1-8e1207631c12"/>
+    <ds:schemaRef ds:uri="a97c5eaf-f6f2-424c-b1de-d58a88ab7d7b"/>
+    <ds:schemaRef ds:uri="fa6a9aea-fb0f-4ddd-aff8-712634b7d5fe"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6B1DF434-1788-4B9D-A37D-453840EA7450}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="fa6a9aea-fb0f-4ddd-aff8-712634b7d5fe"/>
+    <ds:schemaRef ds:uri="797d4723-7e88-4c98-a7d1-8e1207631c12"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{05480E7E-AD73-46FA-B13F-FF6721C77631}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>